--- a/grupos/4ARHV - Estadisticos 20222.xlsx
+++ b/grupos/4ARHV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="139">
   <si>
     <t>Materia</t>
   </si>
@@ -180,16 +180,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Desc Desc Desc</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Gomez Lopez Javier</t>
-  </si>
-  <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
     <t>Camacho Juárez Sergio Eduardo</t>
@@ -927,7 +927,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -981,7 +981,7 @@
         <v>5</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -1004,7 +1004,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>9</v>
@@ -1058,7 +1058,7 @@
         <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -1081,7 +1081,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -1126,7 +1126,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1146,7 +1146,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1223,7 +1223,7 @@
         <v>4</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1277,7 +1277,7 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1300,7 +1300,7 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>9</v>
@@ -1354,7 +1354,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1377,7 +1377,7 @@
         <v>4</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -1431,7 +1431,7 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -1454,7 +1454,7 @@
         <v>4</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -1508,7 +1508,7 @@
         <v>5</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -1531,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>9</v>
@@ -1585,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1608,7 +1608,7 @@
         <v>5</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>8</v>
@@ -1662,7 +1662,7 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1685,7 +1685,7 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>7</v>
@@ -1739,7 +1739,7 @@
         <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1762,7 +1762,7 @@
         <v>8</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -1816,7 +1816,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1839,7 +1839,7 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E16">
         <v>10</v>
@@ -1893,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1916,7 +1916,7 @@
         <v>6</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <v>9</v>
@@ -1970,7 +1970,7 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -1993,7 +1993,7 @@
         <v>5</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>8</v>
@@ -2047,7 +2047,7 @@
         <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2070,7 +2070,7 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>9</v>
@@ -2124,7 +2124,7 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2147,7 +2147,7 @@
         <v>6</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>9</v>
@@ -2201,7 +2201,7 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2224,7 +2224,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>8</v>
@@ -2278,7 +2278,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2301,7 +2301,7 @@
         <v>5</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>6</v>
@@ -2355,7 +2355,7 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2378,7 +2378,7 @@
         <v>8</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>10</v>
@@ -2432,7 +2432,7 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2455,7 +2455,7 @@
         <v>8</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>9</v>
@@ -2509,7 +2509,7 @@
         <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2532,7 +2532,7 @@
         <v>4</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E25">
         <v>5</v>
@@ -2586,7 +2586,7 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2609,7 +2609,7 @@
         <v>5</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>8</v>
@@ -2663,7 +2663,7 @@
         <v>5</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2686,7 +2686,7 @@
         <v>5</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <v>7</v>
@@ -2740,7 +2740,7 @@
         <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2763,7 +2763,7 @@
         <v>5</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>8</v>
@@ -2817,7 +2817,7 @@
         <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -2840,7 +2840,7 @@
         <v>5</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>8</v>
@@ -2894,7 +2894,7 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -2971,7 +2971,7 @@
         <v>5</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -2994,7 +2994,7 @@
         <v>5</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E31">
         <v>8</v>
@@ -3048,7 +3048,7 @@
         <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3071,7 +3071,7 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E32">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -3258,7 +3258,7 @@
         <v>150</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>86</v>
@@ -3317,7 +3317,7 @@
         <v>150</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -3376,7 +3376,7 @@
         <v>150</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -3426,7 +3426,7 @@
         <v>150</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E7">
         <v>88</v>
@@ -3485,7 +3485,7 @@
         <v>150</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E8">
         <v>80</v>
@@ -3544,7 +3544,7 @@
         <v>150</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -3603,7 +3603,7 @@
         <v>150</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E10">
         <v>88</v>
@@ -3662,7 +3662,7 @@
         <v>150</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E11">
         <v>74</v>
@@ -3721,7 +3721,7 @@
         <v>150</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>96</v>
@@ -3780,7 +3780,7 @@
         <v>150</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>88</v>
@@ -3839,7 +3839,7 @@
         <v>150</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E14">
         <v>72</v>
@@ -3898,7 +3898,7 @@
         <v>150</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E15">
         <v>92</v>
@@ -3957,7 +3957,7 @@
         <v>150</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -4016,7 +4016,7 @@
         <v>150</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E17">
         <v>82</v>
@@ -4075,7 +4075,7 @@
         <v>150</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E18">
         <v>90</v>
@@ -4134,7 +4134,7 @@
         <v>150</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -4193,7 +4193,7 @@
         <v>150</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -4252,7 +4252,7 @@
         <v>150</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E21">
         <v>98</v>
@@ -4311,7 +4311,7 @@
         <v>150</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E22">
         <v>76</v>
@@ -4370,7 +4370,7 @@
         <v>150</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -4429,7 +4429,7 @@
         <v>150</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -4488,7 +4488,7 @@
         <v>75</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E25">
         <v>28</v>
@@ -4547,7 +4547,7 @@
         <v>150</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E26">
         <v>94</v>
@@ -4606,7 +4606,7 @@
         <v>150</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E27">
         <v>92</v>
@@ -4665,7 +4665,7 @@
         <v>150</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -4724,7 +4724,7 @@
         <v>150</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -4783,7 +4783,7 @@
         <v>150</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E30">
         <v>100</v>
@@ -4842,7 +4842,7 @@
         <v>150</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E31">
         <v>84</v>
@@ -4901,7 +4901,7 @@
         <v>150</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E32">
         <v>86</v>
@@ -5001,7 +5001,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -5030,13 +5030,13 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -5051,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J3">
         <v>100</v>
@@ -5059,36 +5059,39 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>41.38</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>58.62</v>
+      </c>
+      <c r="H4">
+        <v>6.1</v>
       </c>
       <c r="I4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -5097,19 +5100,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>41.38</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G5">
-        <v>58.62</v>
+        <v>17.24</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5189,7 +5192,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5230,7 +5233,7 @@
         <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>53</v>
@@ -5250,7 +5253,7 @@
         <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
@@ -5258,22 +5261,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920029</v>
+        <v>21330051920031</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5290,167 +5293,167 @@
         <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920031</v>
+        <v>19330051920361</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920031</v>
+        <v>21330051920034</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920361</v>
+        <v>21330051920034</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920361</v>
+        <v>20330051920117</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920034</v>
+        <v>20330051920117</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920034</v>
+        <v>21330051920035</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920034</v>
+        <v>21330051920035</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920117</v>
+        <v>21330051920036</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>53</v>
@@ -5458,19 +5461,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920117</v>
+        <v>21330051920036</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>54</v>
@@ -5478,99 +5481,99 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920117</v>
+        <v>21330051920037</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920035</v>
+        <v>21330051920037</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920035</v>
+        <v>21330051920038</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920035</v>
+        <v>21330051920038</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920036</v>
+        <v>21330051920390</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
         <v>53</v>
@@ -5578,19 +5581,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920036</v>
+        <v>21330051920390</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>54</v>
@@ -5598,99 +5601,99 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920036</v>
+        <v>21330051920040</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920037</v>
+        <v>21330051920040</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920037</v>
+        <v>21330051920041</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920037</v>
+        <v>21330051920041</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920038</v>
+        <v>21330051920043</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
         <v>53</v>
@@ -5698,19 +5701,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920038</v>
+        <v>21330051920043</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
         <v>54</v>
@@ -5718,99 +5721,99 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920038</v>
+        <v>21330051920045</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920390</v>
+        <v>21330051920045</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920390</v>
+        <v>21330051920046</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920390</v>
+        <v>21330051920046</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920040</v>
+        <v>21330051920047</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
         <v>53</v>
@@ -5818,19 +5821,19 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920040</v>
+        <v>21330051920047</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
         <v>54</v>
@@ -5838,99 +5841,99 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920040</v>
+        <v>21330051920050</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D33" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920041</v>
+        <v>21330051920050</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D34" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920041</v>
+        <v>21330051920051</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D35" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920041</v>
+        <v>21330051920051</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920043</v>
+        <v>21330051920054</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E37" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
         <v>53</v>
@@ -5938,19 +5941,19 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920043</v>
+        <v>21330051920054</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F38" t="s">
         <v>54</v>
@@ -5958,99 +5961,99 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920043</v>
+        <v>21330051920055</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920045</v>
+        <v>21330051920055</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920045</v>
+        <v>21330051920056</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C41" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D41" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920045</v>
+        <v>21330051920056</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920046</v>
+        <v>21330051920057</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D43" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E43" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F43" t="s">
         <v>53</v>
@@ -6058,19 +6061,19 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920046</v>
+        <v>21330051920057</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E44" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
         <v>54</v>
@@ -6078,99 +6081,99 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920046</v>
+        <v>21330051920058</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D45" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920047</v>
+        <v>21330051920058</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D46" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E46" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920047</v>
+        <v>21330051920059</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="D47" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>21330051920047</v>
+        <v>21330051920059</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>21330051920050</v>
+        <v>21330051920060</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D49" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E49" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F49" t="s">
         <v>53</v>
@@ -6178,19 +6181,19 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>21330051920050</v>
+        <v>21330051920060</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C50" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D50" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E50" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
         <v>54</v>
@@ -6198,99 +6201,99 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>21330051920050</v>
+        <v>21330051920062</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D51" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>21330051920051</v>
+        <v>21330051920062</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="D52" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>21330051920051</v>
+        <v>21330051920063</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D53" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>21330051920051</v>
+        <v>21330051920063</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C54" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D54" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>21330051920054</v>
+        <v>21330051920065</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C55" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D55" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E55" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F55" t="s">
         <v>53</v>
@@ -6298,19 +6301,19 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>21330051920054</v>
+        <v>21330051920065</v>
       </c>
       <c r="B56" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D56" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E56" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F56" t="s">
         <v>54</v>
@@ -6318,622 +6321,42 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>21330051920054</v>
+        <v>21330051920067</v>
       </c>
       <c r="B57" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C57" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D57" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F57" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>21330051920055</v>
+        <v>21330051920067</v>
       </c>
       <c r="B58" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D58" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E58" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920055</v>
-      </c>
-      <c r="B59" t="s">
-        <v>81</v>
-      </c>
-      <c r="C59" t="s">
-        <v>104</v>
-      </c>
-      <c r="D59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920055</v>
-      </c>
-      <c r="B60" t="s">
-        <v>81</v>
-      </c>
-      <c r="C60" t="s">
-        <v>104</v>
-      </c>
-      <c r="D60" t="s">
-        <v>129</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920056</v>
-      </c>
-      <c r="B61" t="s">
-        <v>82</v>
-      </c>
-      <c r="C61" t="s">
-        <v>105</v>
-      </c>
-      <c r="D61" t="s">
-        <v>130</v>
-      </c>
-      <c r="E61" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920056</v>
-      </c>
-      <c r="B62" t="s">
-        <v>82</v>
-      </c>
-      <c r="C62" t="s">
-        <v>105</v>
-      </c>
-      <c r="D62" t="s">
-        <v>130</v>
-      </c>
-      <c r="E62" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920056</v>
-      </c>
-      <c r="B63" t="s">
-        <v>82</v>
-      </c>
-      <c r="C63" t="s">
-        <v>105</v>
-      </c>
-      <c r="D63" t="s">
-        <v>130</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920057</v>
-      </c>
-      <c r="B64" t="s">
-        <v>83</v>
-      </c>
-      <c r="C64" t="s">
-        <v>75</v>
-      </c>
-      <c r="D64" t="s">
-        <v>131</v>
-      </c>
-      <c r="E64" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920057</v>
-      </c>
-      <c r="B65" t="s">
-        <v>83</v>
-      </c>
-      <c r="C65" t="s">
-        <v>75</v>
-      </c>
-      <c r="D65" t="s">
-        <v>131</v>
-      </c>
-      <c r="E65" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920057</v>
-      </c>
-      <c r="B66" t="s">
-        <v>83</v>
-      </c>
-      <c r="C66" t="s">
-        <v>75</v>
-      </c>
-      <c r="D66" t="s">
-        <v>131</v>
-      </c>
-      <c r="E66" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920058</v>
-      </c>
-      <c r="B67" t="s">
-        <v>84</v>
-      </c>
-      <c r="C67" t="s">
-        <v>75</v>
-      </c>
-      <c r="D67" t="s">
-        <v>132</v>
-      </c>
-      <c r="E67" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920058</v>
-      </c>
-      <c r="B68" t="s">
-        <v>84</v>
-      </c>
-      <c r="C68" t="s">
-        <v>75</v>
-      </c>
-      <c r="D68" t="s">
-        <v>132</v>
-      </c>
-      <c r="E68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920058</v>
-      </c>
-      <c r="B69" t="s">
-        <v>84</v>
-      </c>
-      <c r="C69" t="s">
-        <v>75</v>
-      </c>
-      <c r="D69" t="s">
-        <v>132</v>
-      </c>
-      <c r="E69" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920059</v>
-      </c>
-      <c r="B70" t="s">
-        <v>85</v>
-      </c>
-      <c r="C70" t="s">
-        <v>106</v>
-      </c>
-      <c r="D70" t="s">
-        <v>133</v>
-      </c>
-      <c r="E70" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920059</v>
-      </c>
-      <c r="B71" t="s">
-        <v>85</v>
-      </c>
-      <c r="C71" t="s">
-        <v>106</v>
-      </c>
-      <c r="D71" t="s">
-        <v>133</v>
-      </c>
-      <c r="E71" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920059</v>
-      </c>
-      <c r="B72" t="s">
-        <v>85</v>
-      </c>
-      <c r="C72" t="s">
-        <v>106</v>
-      </c>
-      <c r="D72" t="s">
-        <v>133</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920060</v>
-      </c>
-      <c r="B73" t="s">
-        <v>83</v>
-      </c>
-      <c r="C73" t="s">
-        <v>107</v>
-      </c>
-      <c r="D73" t="s">
-        <v>134</v>
-      </c>
-      <c r="E73" t="s">
-        <v>7</v>
-      </c>
-      <c r="F73" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920060</v>
-      </c>
-      <c r="B74" t="s">
-        <v>83</v>
-      </c>
-      <c r="C74" t="s">
-        <v>107</v>
-      </c>
-      <c r="D74" t="s">
-        <v>134</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920060</v>
-      </c>
-      <c r="B75" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" t="s">
-        <v>107</v>
-      </c>
-      <c r="D75" t="s">
-        <v>134</v>
-      </c>
-      <c r="E75" t="s">
-        <v>10</v>
-      </c>
-      <c r="F75" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920062</v>
-      </c>
-      <c r="B76" t="s">
-        <v>86</v>
-      </c>
-      <c r="C76" t="s">
-        <v>83</v>
-      </c>
-      <c r="D76" t="s">
-        <v>135</v>
-      </c>
-      <c r="E76" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920062</v>
-      </c>
-      <c r="B77" t="s">
-        <v>86</v>
-      </c>
-      <c r="C77" t="s">
-        <v>83</v>
-      </c>
-      <c r="D77" t="s">
-        <v>135</v>
-      </c>
-      <c r="E77" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920062</v>
-      </c>
-      <c r="B78" t="s">
-        <v>86</v>
-      </c>
-      <c r="C78" t="s">
-        <v>83</v>
-      </c>
-      <c r="D78" t="s">
-        <v>135</v>
-      </c>
-      <c r="E78" t="s">
-        <v>10</v>
-      </c>
-      <c r="F78" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920063</v>
-      </c>
-      <c r="B79" t="s">
-        <v>87</v>
-      </c>
-      <c r="C79" t="s">
-        <v>108</v>
-      </c>
-      <c r="D79" t="s">
-        <v>136</v>
-      </c>
-      <c r="E79" t="s">
-        <v>7</v>
-      </c>
-      <c r="F79" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920063</v>
-      </c>
-      <c r="B80" t="s">
-        <v>87</v>
-      </c>
-      <c r="C80" t="s">
-        <v>108</v>
-      </c>
-      <c r="D80" t="s">
-        <v>136</v>
-      </c>
-      <c r="E80" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920063</v>
-      </c>
-      <c r="B81" t="s">
-        <v>87</v>
-      </c>
-      <c r="C81" t="s">
-        <v>108</v>
-      </c>
-      <c r="D81" t="s">
-        <v>136</v>
-      </c>
-      <c r="E81" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920065</v>
-      </c>
-      <c r="B82" t="s">
-        <v>88</v>
-      </c>
-      <c r="C82" t="s">
-        <v>99</v>
-      </c>
-      <c r="D82" t="s">
-        <v>137</v>
-      </c>
-      <c r="E82" t="s">
-        <v>7</v>
-      </c>
-      <c r="F82" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920065</v>
-      </c>
-      <c r="B83" t="s">
-        <v>88</v>
-      </c>
-      <c r="C83" t="s">
-        <v>99</v>
-      </c>
-      <c r="D83" t="s">
-        <v>137</v>
-      </c>
-      <c r="E83" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920065</v>
-      </c>
-      <c r="B84" t="s">
-        <v>88</v>
-      </c>
-      <c r="C84" t="s">
-        <v>99</v>
-      </c>
-      <c r="D84" t="s">
-        <v>137</v>
-      </c>
-      <c r="E84" t="s">
-        <v>10</v>
-      </c>
-      <c r="F84" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051920067</v>
-      </c>
-      <c r="B85" t="s">
-        <v>89</v>
-      </c>
-      <c r="C85" t="s">
-        <v>109</v>
-      </c>
-      <c r="D85" t="s">
-        <v>138</v>
-      </c>
-      <c r="E85" t="s">
-        <v>7</v>
-      </c>
-      <c r="F85" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>21330051920067</v>
-      </c>
-      <c r="B86" t="s">
-        <v>89</v>
-      </c>
-      <c r="C86" t="s">
-        <v>109</v>
-      </c>
-      <c r="D86" t="s">
-        <v>138</v>
-      </c>
-      <c r="E86" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>21330051920067</v>
-      </c>
-      <c r="B87" t="s">
-        <v>89</v>
-      </c>
-      <c r="C87" t="s">
-        <v>109</v>
-      </c>
-      <c r="D87" t="s">
-        <v>138</v>
-      </c>
-      <c r="E87" t="s">
-        <v>10</v>
-      </c>
-      <c r="F87" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -6981,7 +6404,7 @@
         <v>110</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6998,7 +6421,7 @@
         <v>111</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7015,7 +6438,7 @@
         <v>113</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7032,7 +6455,7 @@
         <v>114</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7049,7 +6472,7 @@
         <v>115</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7066,7 +6489,7 @@
         <v>116</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7083,7 +6506,7 @@
         <v>117</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7100,7 +6523,7 @@
         <v>118</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7117,7 +6540,7 @@
         <v>119</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7134,7 +6557,7 @@
         <v>120</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7151,7 +6574,7 @@
         <v>121</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7168,7 +6591,7 @@
         <v>122</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7185,7 +6608,7 @@
         <v>123</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7202,7 +6625,7 @@
         <v>124</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7219,7 +6642,7 @@
         <v>125</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7236,7 +6659,7 @@
         <v>126</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7253,7 +6676,7 @@
         <v>127</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -7270,7 +6693,7 @@
         <v>128</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -7287,7 +6710,7 @@
         <v>129</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -7304,7 +6727,7 @@
         <v>130</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7321,7 +6744,7 @@
         <v>131</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -7338,7 +6761,7 @@
         <v>132</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -7355,7 +6778,7 @@
         <v>133</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7372,7 +6795,7 @@
         <v>134</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7389,7 +6812,7 @@
         <v>135</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7406,7 +6829,7 @@
         <v>136</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -7423,7 +6846,7 @@
         <v>137</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7440,7 +6863,7 @@
         <v>138</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7457,7 +6880,7 @@
         <v>112</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7467,7 +6890,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7499,19 +6922,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920361</v>
+        <v>21330051920034</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>53</v>
@@ -7522,24 +6945,507 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920361</v>
+        <v>21330051920034</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
       </c>
       <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920038</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920038</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920041</v>
+      </c>
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920041</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920043</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920043</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920045</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920045</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920047</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920047</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920050</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920050</v>
+      </c>
+      <c r="B15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920051</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920051</v>
+      </c>
+      <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920055</v>
+      </c>
+      <c r="B18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920055</v>
+      </c>
+      <c r="B19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920056</v>
+      </c>
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920056</v>
+      </c>
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920065</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>137</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920065</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>19330051920361</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20222.xlsx
+++ b/grupos/4ARHV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="139">
   <si>
     <t>Materia</t>
   </si>
@@ -180,22 +180,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Gomez Lopez Javier</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
     <t>Desc Desc Desc</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Gomez Lopez Javier</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
     <t>NC</t>
@@ -933,10 +933,10 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -987,10 +987,10 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1010,10 +1010,10 @@
         <v>9</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1064,10 +1064,10 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1087,7 +1087,7 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1132,7 +1132,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1152,10 +1152,10 @@
         <v>8</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1206,10 +1206,10 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1229,10 +1229,10 @@
         <v>5</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1283,10 +1283,10 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1306,10 +1306,10 @@
         <v>9</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1360,10 +1360,10 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1383,10 +1383,10 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1437,10 +1437,10 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1460,10 +1460,10 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1514,10 +1514,10 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1537,10 +1537,10 @@
         <v>9</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1591,10 +1591,10 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1614,10 +1614,10 @@
         <v>8</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1668,10 +1668,10 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1691,10 +1691,10 @@
         <v>7</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1745,10 +1745,10 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1768,10 +1768,10 @@
         <v>7</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1822,10 +1822,10 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1845,10 +1845,10 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1899,10 +1899,10 @@
         <v>10</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1922,10 +1922,10 @@
         <v>9</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -1976,10 +1976,10 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1999,10 +1999,10 @@
         <v>8</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2053,10 +2053,10 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2076,10 +2076,10 @@
         <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2130,10 +2130,10 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2207,10 +2207,10 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2230,10 +2230,10 @@
         <v>8</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2284,10 +2284,10 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2307,10 +2307,10 @@
         <v>6</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2361,10 +2361,10 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2384,10 +2384,10 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2438,10 +2438,10 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2515,10 +2515,10 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2538,10 +2538,10 @@
         <v>5</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2592,10 +2592,10 @@
         <v>5</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2615,10 +2615,10 @@
         <v>8</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2669,10 +2669,10 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2692,10 +2692,10 @@
         <v>7</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2746,10 +2746,10 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2769,10 +2769,10 @@
         <v>8</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2823,10 +2823,10 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2846,10 +2846,10 @@
         <v>8</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -2900,10 +2900,10 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2923,10 +2923,10 @@
         <v>8</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -2977,10 +2977,10 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3000,10 +3000,10 @@
         <v>8</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3054,10 +3054,10 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3077,10 +3077,10 @@
         <v>8</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3131,10 +3131,10 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3264,10 +3264,10 @@
         <v>86</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -3323,10 +3323,10 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -3382,7 +3382,7 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -3432,10 +3432,10 @@
         <v>88</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -3491,10 +3491,10 @@
         <v>80</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -3550,10 +3550,10 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3609,10 +3609,10 @@
         <v>88</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3668,10 +3668,10 @@
         <v>74</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -3727,10 +3727,10 @@
         <v>96</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -3786,10 +3786,10 @@
         <v>88</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>72</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -3904,10 +3904,10 @@
         <v>92</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -3963,10 +3963,10 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>82</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -4081,10 +4081,10 @@
         <v>90</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -4140,10 +4140,10 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -4199,10 +4199,10 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -4258,10 +4258,10 @@
         <v>98</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -4317,10 +4317,10 @@
         <v>76</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -4376,10 +4376,10 @@
         <v>100</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -4435,10 +4435,10 @@
         <v>100</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -4494,10 +4494,10 @@
         <v>28</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -4553,10 +4553,10 @@
         <v>94</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -4612,10 +4612,10 @@
         <v>92</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -4671,10 +4671,10 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -4730,10 +4730,10 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -4789,10 +4789,10 @@
         <v>100</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -4848,10 +4848,10 @@
         <v>84</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -4907,10 +4907,10 @@
         <v>86</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -5001,7 +5001,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -5010,77 +5010,83 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>41.38</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>58.62</v>
+      </c>
+      <c r="H2">
+        <v>6.1</v>
       </c>
       <c r="I2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>17.24</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
       </c>
       <c r="I3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>41.38</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="G4">
-        <v>58.62</v>
+        <v>10.71</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5091,7 +5097,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -5100,19 +5106,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>82.76000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="G5">
-        <v>17.24</v>
+        <v>10.34</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5123,7 +5129,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -5132,19 +5138,19 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>89.66</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G6">
-        <v>10.34</v>
+        <v>6.9</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5155,7 +5161,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -5164,19 +5170,19 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>93.09999999999999</v>
+        <v>96.55</v>
       </c>
       <c r="G7">
-        <v>6.9</v>
+        <v>3.45</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>6.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5192,7 +5198,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5217,1146 +5223,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920029</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920029</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920031</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920031</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920361</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920034</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920034</v>
-      </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920117</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920117</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920035</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920035</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920036</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920036</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920037</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920037</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920038</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>95</v>
-      </c>
-      <c r="D17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920038</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920390</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19" t="s">
-        <v>119</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920390</v>
-      </c>
-      <c r="B20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" t="s">
-        <v>96</v>
-      </c>
-      <c r="D20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920040</v>
-      </c>
-      <c r="B21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920040</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920041</v>
-      </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920041</v>
-      </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" t="s">
-        <v>121</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920043</v>
-      </c>
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" t="s">
-        <v>98</v>
-      </c>
-      <c r="D25" t="s">
-        <v>122</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920043</v>
-      </c>
-      <c r="B26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" t="s">
-        <v>122</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920045</v>
-      </c>
-      <c r="B27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920045</v>
-      </c>
-      <c r="B28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" t="s">
-        <v>123</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920046</v>
-      </c>
-      <c r="B29" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" t="s">
-        <v>124</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920046</v>
-      </c>
-      <c r="B30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" t="s">
-        <v>124</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920047</v>
-      </c>
-      <c r="B31" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" t="s">
-        <v>125</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920047</v>
-      </c>
-      <c r="B32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920050</v>
-      </c>
-      <c r="B33" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" t="s">
-        <v>126</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920050</v>
-      </c>
-      <c r="B34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" t="s">
-        <v>126</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920051</v>
-      </c>
-      <c r="B35" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" t="s">
-        <v>127</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920051</v>
-      </c>
-      <c r="B36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" t="s">
-        <v>102</v>
-      </c>
-      <c r="D36" t="s">
-        <v>127</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920054</v>
-      </c>
-      <c r="B37" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>128</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920054</v>
-      </c>
-      <c r="B38" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" t="s">
-        <v>103</v>
-      </c>
-      <c r="D38" t="s">
-        <v>128</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920055</v>
-      </c>
-      <c r="B39" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" t="s">
-        <v>129</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920055</v>
-      </c>
-      <c r="B40" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" t="s">
-        <v>129</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920056</v>
-      </c>
-      <c r="B41" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" t="s">
-        <v>105</v>
-      </c>
-      <c r="D41" t="s">
-        <v>130</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920056</v>
-      </c>
-      <c r="B42" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" t="s">
-        <v>105</v>
-      </c>
-      <c r="D42" t="s">
-        <v>130</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920057</v>
-      </c>
-      <c r="B43" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" t="s">
-        <v>75</v>
-      </c>
-      <c r="D43" t="s">
-        <v>131</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920057</v>
-      </c>
-      <c r="B44" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" t="s">
-        <v>75</v>
-      </c>
-      <c r="D44" t="s">
-        <v>131</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920058</v>
-      </c>
-      <c r="B45" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" t="s">
-        <v>132</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920058</v>
-      </c>
-      <c r="B46" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" t="s">
-        <v>75</v>
-      </c>
-      <c r="D46" t="s">
-        <v>132</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920059</v>
-      </c>
-      <c r="B47" t="s">
-        <v>85</v>
-      </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" t="s">
-        <v>133</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920059</v>
-      </c>
-      <c r="B48" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" t="s">
-        <v>106</v>
-      </c>
-      <c r="D48" t="s">
-        <v>133</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920060</v>
-      </c>
-      <c r="B49" t="s">
-        <v>83</v>
-      </c>
-      <c r="C49" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" t="s">
-        <v>134</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920060</v>
-      </c>
-      <c r="B50" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" t="s">
-        <v>134</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920062</v>
-      </c>
-      <c r="B51" t="s">
-        <v>86</v>
-      </c>
-      <c r="C51" t="s">
-        <v>83</v>
-      </c>
-      <c r="D51" t="s">
-        <v>135</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920062</v>
-      </c>
-      <c r="B52" t="s">
-        <v>86</v>
-      </c>
-      <c r="C52" t="s">
-        <v>83</v>
-      </c>
-      <c r="D52" t="s">
-        <v>135</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920063</v>
-      </c>
-      <c r="B53" t="s">
-        <v>87</v>
-      </c>
-      <c r="C53" t="s">
-        <v>108</v>
-      </c>
-      <c r="D53" t="s">
-        <v>136</v>
-      </c>
-      <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920063</v>
-      </c>
-      <c r="B54" t="s">
-        <v>87</v>
-      </c>
-      <c r="C54" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" t="s">
-        <v>136</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920065</v>
-      </c>
-      <c r="B55" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" t="s">
-        <v>99</v>
-      </c>
-      <c r="D55" t="s">
-        <v>137</v>
-      </c>
-      <c r="E55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920065</v>
-      </c>
-      <c r="B56" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" t="s">
-        <v>99</v>
-      </c>
-      <c r="D56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E56" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920067</v>
-      </c>
-      <c r="B57" t="s">
-        <v>89</v>
-      </c>
-      <c r="C57" t="s">
-        <v>109</v>
-      </c>
-      <c r="D57" t="s">
-        <v>138</v>
-      </c>
-      <c r="E57" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920067</v>
-      </c>
-      <c r="B58" t="s">
-        <v>89</v>
-      </c>
-      <c r="C58" t="s">
-        <v>109</v>
-      </c>
-      <c r="D58" t="s">
-        <v>138</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -6404,7 +5270,7 @@
         <v>110</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6421,466 +5287,466 @@
         <v>111</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920034</v>
+        <v>19330051920361</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920117</v>
+        <v>21330051920034</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920035</v>
+        <v>20330051920117</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920036</v>
+        <v>21330051920035</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920037</v>
+        <v>21330051920036</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920038</v>
+        <v>21330051920037</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920390</v>
+        <v>21330051920038</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920040</v>
+        <v>21330051920390</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920041</v>
+        <v>21330051920040</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920043</v>
+        <v>21330051920041</v>
       </c>
       <c r="B13" t="s">
         <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920045</v>
+        <v>21330051920043</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920046</v>
+        <v>21330051920045</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920047</v>
+        <v>21330051920046</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920050</v>
+        <v>21330051920047</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920051</v>
+        <v>21330051920050</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920054</v>
+        <v>21330051920051</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920055</v>
+        <v>21330051920054</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920056</v>
+        <v>21330051920055</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920057</v>
+        <v>21330051920056</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920058</v>
+        <v>21330051920057</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
         <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920059</v>
+        <v>21330051920058</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920060</v>
+        <v>21330051920059</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920062</v>
+        <v>21330051920060</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920063</v>
+        <v>21330051920062</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920065</v>
+        <v>21330051920063</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920067</v>
+        <v>21330051920065</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920361</v>
+        <v>21330051920067</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6890,7 +5756,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6922,531 +5788,301 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920034</v>
+        <v>21330051920036</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>53</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920034</v>
+        <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920038</v>
+        <v>21330051920029</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>53</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920038</v>
+        <v>21330051920031</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920041</v>
+        <v>21330051920035</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>53</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920041</v>
+        <v>21330051920390</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920043</v>
+        <v>21330051920046</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920043</v>
+        <v>21330051920057</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920045</v>
+        <v>21330051920059</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>53</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920045</v>
+        <v>21330051920060</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920047</v>
+        <v>21330051920062</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>53</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920047</v>
+        <v>21330051920063</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920050</v>
+        <v>21330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
         <v>53</v>
       </c>
       <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920050</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920051</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920051</v>
-      </c>
-      <c r="B17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920055</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920055</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920056</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920056</v>
-      </c>
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920065</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920065</v>
-      </c>
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920361</v>
-      </c>
-      <c r="B24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ARHV - Estadisticos 20222.xlsx
+++ b/grupos/4ARHV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="143">
   <si>
     <t>Materia</t>
   </si>
@@ -105,6 +105,9 @@
     <t>JUAREZ JUAREZ NUBIA NAHOMI</t>
   </si>
   <si>
+    <t>MARTINEZ JIMENEZ MICHEL</t>
+  </si>
+  <si>
     <t>MAYAHUA TETLACTLE OSCAR</t>
   </si>
   <si>
@@ -192,12 +195,12 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Desc Desc Desc</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -208,6 +211,15 @@
   </si>
   <si>
     <t>Nombres</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
   </si>
   <si>
     <t>ANDRADE</t>
@@ -793,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:Y33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -2141,22 +2153,22 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="G20">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2195,22 +2207,22 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2221,19 +2233,19 @@
         <v>10</v>
       </c>
       <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21">
         <v>7</v>
       </c>
-      <c r="D21">
-        <v>8</v>
-      </c>
       <c r="E21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2275,19 +2287,19 @@
         <v>10</v>
       </c>
       <c r="U21">
+        <v>6</v>
+      </c>
+      <c r="V21">
         <v>7</v>
       </c>
-      <c r="V21">
-        <v>8</v>
-      </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2295,22 +2307,22 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F22">
         <v>6</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2349,22 +2361,22 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2372,22 +2384,22 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2426,22 +2438,22 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2458,10 +2470,10 @@
         <v>8</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G24">
         <v>9</v>
@@ -2512,10 +2524,10 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2526,22 +2538,22 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F25">
         <v>6</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2580,22 +2592,22 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2603,22 +2615,22 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F26">
         <v>6</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2657,22 +2669,22 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>5</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2680,76 +2692,76 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27">
         <v>5</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27">
+        <v>8</v>
+      </c>
+      <c r="F27">
+        <v>6</v>
+      </c>
+      <c r="G27">
+        <v>6</v>
+      </c>
+      <c r="H27">
+        <v>-1</v>
+      </c>
+      <c r="I27">
+        <v>-1</v>
+      </c>
+      <c r="J27">
+        <v>-1</v>
+      </c>
+      <c r="K27">
+        <v>-1</v>
+      </c>
+      <c r="L27">
+        <v>-1</v>
+      </c>
+      <c r="M27">
+        <v>-1</v>
+      </c>
+      <c r="N27">
+        <v>-1</v>
+      </c>
+      <c r="O27">
+        <v>-1</v>
+      </c>
+      <c r="P27">
+        <v>-1</v>
+      </c>
+      <c r="Q27">
+        <v>-1</v>
+      </c>
+      <c r="R27">
+        <v>-1</v>
+      </c>
+      <c r="S27">
+        <v>-1</v>
+      </c>
+      <c r="T27">
         <v>7</v>
       </c>
-      <c r="F27">
-        <v>6</v>
-      </c>
-      <c r="G27">
-        <v>8</v>
-      </c>
-      <c r="H27">
-        <v>-1</v>
-      </c>
-      <c r="I27">
-        <v>-1</v>
-      </c>
-      <c r="J27">
-        <v>-1</v>
-      </c>
-      <c r="K27">
-        <v>-1</v>
-      </c>
-      <c r="L27">
-        <v>-1</v>
-      </c>
-      <c r="M27">
-        <v>-1</v>
-      </c>
-      <c r="N27">
-        <v>-1</v>
-      </c>
-      <c r="O27">
-        <v>-1</v>
-      </c>
-      <c r="P27">
-        <v>-1</v>
-      </c>
-      <c r="Q27">
-        <v>-1</v>
-      </c>
-      <c r="R27">
-        <v>-1</v>
-      </c>
-      <c r="S27">
-        <v>-1</v>
-      </c>
-      <c r="T27">
-        <v>8</v>
-      </c>
       <c r="U27">
         <v>5</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2757,22 +2769,22 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28">
         <v>5</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F28">
         <v>6</v>
       </c>
       <c r="G28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2811,22 +2823,22 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>5</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2840,7 +2852,7 @@
         <v>5</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>8</v>
@@ -2894,7 +2906,7 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -2917,7 +2929,7 @@
         <v>5</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -2971,7 +2983,7 @@
         <v>5</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -2988,23 +3000,23 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>5</v>
       </c>
       <c r="D31">
+        <v>8</v>
+      </c>
+      <c r="E31">
+        <v>8</v>
+      </c>
+      <c r="F31">
+        <v>6</v>
+      </c>
+      <c r="G31">
         <v>9</v>
       </c>
-      <c r="E31">
-        <v>8</v>
-      </c>
-      <c r="F31">
-        <v>6</v>
-      </c>
-      <c r="G31">
-        <v>8</v>
-      </c>
       <c r="H31">
         <v>-1</v>
       </c>
@@ -3042,22 +3054,22 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>5</v>
       </c>
       <c r="V31">
+        <v>8</v>
+      </c>
+      <c r="W31">
+        <v>8</v>
+      </c>
+      <c r="X31">
+        <v>6</v>
+      </c>
+      <c r="Y31">
         <v>9</v>
-      </c>
-      <c r="W31">
-        <v>8</v>
-      </c>
-      <c r="X31">
-        <v>6</v>
-      </c>
-      <c r="Y31">
-        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3068,10 +3080,10 @@
         <v>8</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E32">
         <v>8</v>
@@ -3080,60 +3092,137 @@
         <v>6</v>
       </c>
       <c r="G32">
+        <v>8</v>
+      </c>
+      <c r="H32">
+        <v>-1</v>
+      </c>
+      <c r="I32">
+        <v>-1</v>
+      </c>
+      <c r="J32">
+        <v>-1</v>
+      </c>
+      <c r="K32">
+        <v>-1</v>
+      </c>
+      <c r="L32">
+        <v>-1</v>
+      </c>
+      <c r="M32">
+        <v>-1</v>
+      </c>
+      <c r="N32">
+        <v>-1</v>
+      </c>
+      <c r="O32">
+        <v>-1</v>
+      </c>
+      <c r="P32">
+        <v>-1</v>
+      </c>
+      <c r="Q32">
+        <v>-1</v>
+      </c>
+      <c r="R32">
+        <v>-1</v>
+      </c>
+      <c r="S32">
+        <v>-1</v>
+      </c>
+      <c r="T32">
+        <v>8</v>
+      </c>
+      <c r="U32">
+        <v>5</v>
+      </c>
+      <c r="V32">
+        <v>9</v>
+      </c>
+      <c r="W32">
+        <v>8</v>
+      </c>
+      <c r="X32">
+        <v>6</v>
+      </c>
+      <c r="Y32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
+      <c r="A33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>6</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33">
+        <v>8</v>
+      </c>
+      <c r="F33">
+        <v>6</v>
+      </c>
+      <c r="G33">
         <v>7</v>
       </c>
-      <c r="H32">
-        <v>-1</v>
-      </c>
-      <c r="I32">
-        <v>-1</v>
-      </c>
-      <c r="J32">
-        <v>-1</v>
-      </c>
-      <c r="K32">
-        <v>-1</v>
-      </c>
-      <c r="L32">
-        <v>-1</v>
-      </c>
-      <c r="M32">
-        <v>-1</v>
-      </c>
-      <c r="N32">
-        <v>-1</v>
-      </c>
-      <c r="O32">
-        <v>-1</v>
-      </c>
-      <c r="P32">
-        <v>-1</v>
-      </c>
-      <c r="Q32">
-        <v>-1</v>
-      </c>
-      <c r="R32">
-        <v>-1</v>
-      </c>
-      <c r="S32">
-        <v>-1</v>
-      </c>
-      <c r="T32">
-        <v>8</v>
-      </c>
-      <c r="U32">
-        <v>6</v>
-      </c>
-      <c r="V32">
-        <v>8</v>
-      </c>
-      <c r="W32">
-        <v>8</v>
-      </c>
-      <c r="X32">
-        <v>6</v>
-      </c>
-      <c r="Y32">
+      <c r="H33">
+        <v>-1</v>
+      </c>
+      <c r="I33">
+        <v>-1</v>
+      </c>
+      <c r="J33">
+        <v>-1</v>
+      </c>
+      <c r="K33">
+        <v>-1</v>
+      </c>
+      <c r="L33">
+        <v>-1</v>
+      </c>
+      <c r="M33">
+        <v>-1</v>
+      </c>
+      <c r="N33">
+        <v>-1</v>
+      </c>
+      <c r="O33">
+        <v>-1</v>
+      </c>
+      <c r="P33">
+        <v>-1</v>
+      </c>
+      <c r="Q33">
+        <v>-1</v>
+      </c>
+      <c r="R33">
+        <v>-1</v>
+      </c>
+      <c r="S33">
+        <v>-1</v>
+      </c>
+      <c r="T33">
+        <v>8</v>
+      </c>
+      <c r="U33">
+        <v>6</v>
+      </c>
+      <c r="V33">
+        <v>8</v>
+      </c>
+      <c r="W33">
+        <v>8</v>
+      </c>
+      <c r="X33">
+        <v>6</v>
+      </c>
+      <c r="Y33">
         <v>7</v>
       </c>
     </row>
@@ -3150,7 +3239,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3159,7 +3248,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3167,7 +3256,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -3175,7 +3264,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -4187,22 +4276,22 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>151.4</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>113.3</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -4255,13 +4344,13 @@
         <v>90</v>
       </c>
       <c r="E21">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
       </c>
       <c r="G21">
-        <v>93.3</v>
+        <v>113.3</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -4311,16 +4400,16 @@
         <v>150</v>
       </c>
       <c r="D22">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E22">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F22">
         <v>100</v>
       </c>
       <c r="G22">
-        <v>40</v>
+        <v>93.3</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -4370,16 +4459,16 @@
         <v>150</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="F23">
         <v>100</v>
       </c>
       <c r="G23">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -4485,19 +4574,19 @@
         <v>151.4</v>
       </c>
       <c r="C25">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="D25">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>100</v>
       </c>
       <c r="G25">
-        <v>46.7</v>
+        <v>120</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -4544,19 +4633,19 @@
         <v>151.4</v>
       </c>
       <c r="C26">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="D26">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E26">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="F26">
         <v>100</v>
       </c>
       <c r="G26">
-        <v>73.3</v>
+        <v>46.7</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -4609,13 +4698,13 @@
         <v>90</v>
       </c>
       <c r="E27">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F27">
         <v>100</v>
       </c>
       <c r="G27">
-        <v>106.7</v>
+        <v>73.3</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -4668,13 +4757,13 @@
         <v>90</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F28">
         <v>100</v>
       </c>
       <c r="G28">
-        <v>113.3</v>
+        <v>106.7</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -4724,7 +4813,7 @@
         <v>150</v>
       </c>
       <c r="D29">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -4783,7 +4872,7 @@
         <v>150</v>
       </c>
       <c r="D30">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>100</v>
@@ -4792,7 +4881,7 @@
         <v>100</v>
       </c>
       <c r="G30">
-        <v>120</v>
+        <v>113.3</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -4845,13 +4934,13 @@
         <v>90</v>
       </c>
       <c r="E31">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>100</v>
       </c>
       <c r="G31">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -4904,48 +4993,107 @@
         <v>90</v>
       </c>
       <c r="E32">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F32">
         <v>100</v>
       </c>
       <c r="G32">
+        <v>80</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33">
+        <v>151.4</v>
+      </c>
+      <c r="C33">
+        <v>150</v>
+      </c>
+      <c r="D33">
+        <v>90</v>
+      </c>
+      <c r="E33">
+        <v>86</v>
+      </c>
+      <c r="F33">
+        <v>100</v>
+      </c>
+      <c r="G33">
         <v>60</v>
       </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
         <v>0</v>
       </c>
     </row>
@@ -4972,31 +5120,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5004,10 +5152,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2">
         <v>12</v>
@@ -5016,19 +5164,19 @@
         <v>17</v>
       </c>
       <c r="F2">
-        <v>41.38</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>58.62</v>
+        <v>56.67</v>
       </c>
       <c r="H2">
         <v>6.1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5036,10 +5184,10 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>24</v>
@@ -5048,19 +5196,19 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="G3">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="H3">
         <v>7.1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5068,10 +5216,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>25</v>
@@ -5080,19 +5228,19 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>89.29000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="G4">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="H4">
         <v>7.7</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5100,10 +5248,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>26</v>
@@ -5112,77 +5260,77 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <v>89.66</v>
+        <v>86.67</v>
       </c>
       <c r="G5">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="H5">
         <v>8.199999999999999</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="G6">
-        <v>6.9</v>
+        <v>3.33</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>6.1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>28</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>96.55</v>
+        <v>93.33</v>
       </c>
       <c r="G7">
-        <v>3.45</v>
+        <v>6.67</v>
       </c>
       <c r="H7">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5198,7 +5346,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5207,22 +5355,122 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>21330051920048</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>21330051920048</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>21330051920048</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>21330051920048</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>21330051920048</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -5232,7 +5480,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5241,50 +5489,50 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920029</v>
+        <v>21330051920048</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920031</v>
+        <v>21330051920029</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -5292,16 +5540,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920361</v>
+        <v>21330051920031</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -5309,16 +5557,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920034</v>
+        <v>19330051920361</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -5326,16 +5574,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920117</v>
+        <v>21330051920034</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5343,16 +5591,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920035</v>
+        <v>20330051920117</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5360,16 +5608,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920036</v>
+        <v>21330051920035</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5377,16 +5625,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920037</v>
+        <v>21330051920036</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5394,16 +5642,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920038</v>
+        <v>21330051920037</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -5411,16 +5659,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920390</v>
+        <v>21330051920038</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5428,16 +5676,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920040</v>
+        <v>21330051920390</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -5445,16 +5693,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920041</v>
+        <v>21330051920040</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5462,16 +5710,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920043</v>
+        <v>21330051920041</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -5479,16 +5727,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920045</v>
+        <v>21330051920043</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5496,16 +5744,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920046</v>
+        <v>21330051920045</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5513,16 +5761,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920047</v>
+        <v>21330051920046</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5530,16 +5778,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920050</v>
+        <v>21330051920047</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5547,16 +5795,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920051</v>
+        <v>21330051920050</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5564,16 +5812,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920054</v>
+        <v>21330051920051</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5581,16 +5829,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920055</v>
+        <v>21330051920054</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5598,16 +5846,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920056</v>
+        <v>21330051920055</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5615,16 +5863,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920057</v>
+        <v>21330051920056</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5632,16 +5880,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920058</v>
+        <v>21330051920057</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5649,16 +5897,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920059</v>
+        <v>21330051920058</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5666,16 +5914,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920060</v>
+        <v>21330051920059</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5683,16 +5931,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920062</v>
+        <v>21330051920060</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5700,16 +5948,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920063</v>
+        <v>21330051920062</v>
       </c>
       <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
         <v>87</v>
       </c>
-      <c r="C28" t="s">
-        <v>108</v>
-      </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5717,16 +5965,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920065</v>
+        <v>21330051920063</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5734,18 +5982,35 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
+        <v>21330051920065</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
         <v>21330051920067</v>
       </c>
-      <c r="B30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" t="s">
-        <v>138</v>
-      </c>
-      <c r="E30">
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31">
         <v>0</v>
       </c>
     </row>
@@ -5765,22 +6030,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -5791,19 +6056,19 @@
         <v>21330051920036</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5814,19 +6079,19 @@
         <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5837,19 +6102,19 @@
         <v>21330051920029</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5860,19 +6125,19 @@
         <v>21330051920031</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5883,19 +6148,19 @@
         <v>21330051920035</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5906,19 +6171,19 @@
         <v>21330051920390</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5929,19 +6194,19 @@
         <v>21330051920046</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5952,19 +6217,19 @@
         <v>21330051920057</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5975,19 +6240,19 @@
         <v>21330051920059</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5998,19 +6263,19 @@
         <v>21330051920060</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6021,19 +6286,19 @@
         <v>21330051920062</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6044,19 +6309,19 @@
         <v>21330051920063</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6067,19 +6332,19 @@
         <v>21330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G14">
         <v>5</v>

--- a/grupos/4ARHV - Estadisticos 20222.xlsx
+++ b/grupos/4ARHV - Estadisticos 20222.xlsx
@@ -195,7 +195,7 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
     <t>Martínez López Miguel Ángel</t>

--- a/grupos/4ARHV - Estadisticos 20222.xlsx
+++ b/grupos/4ARHV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="96">
   <si>
     <t>Materia</t>
   </si>
@@ -189,6 +188,9 @@
     <t>Gomez Lopez Javier</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -198,9 +200,6 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -228,129 +227,42 @@
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECATL</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>VEGA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECATL</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>CELESTINO</t>
   </si>
   <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
     <t>SIERRA</t>
   </si>
   <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
@@ -369,69 +281,18 @@
     <t>ALESSANDRA</t>
   </si>
   <si>
-    <t>LUZ DEL CARMEN</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>XOCHITL JOSELINE</t>
-  </si>
-  <si>
     <t>GABRIELA ELIZABET</t>
   </si>
   <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
     <t>KARLA JIMENA</t>
   </si>
   <si>
-    <t>ZENON AXXEL</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
-  </si>
-  <si>
     <t>MIA ARANZA</t>
   </si>
   <si>
-    <t>NUBIA NAHOMI</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ANDREA YONETH</t>
-  </si>
-  <si>
     <t>INGRID CRISTEL</t>
   </si>
   <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
     <t>DANIELA</t>
   </si>
   <si>
@@ -442,9 +303,6 @@
   </si>
   <si>
     <t>YAZURI</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
   </si>
   <si>
     <t>HANIA ZARETH</t>
@@ -454,6 +312,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -506,11 +367,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -960,7 +822,7 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -996,7 +858,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -1037,7 +899,7 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1073,7 +935,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1111,7 +973,7 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1179,7 +1041,7 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1215,7 +1077,7 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1256,7 +1118,7 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1333,7 +1195,7 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1410,7 +1272,7 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1446,7 +1308,7 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1487,7 +1349,7 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1523,7 +1385,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1564,7 +1426,7 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1641,7 +1503,7 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1718,7 +1580,7 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1754,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1795,7 +1657,7 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1831,7 +1693,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1872,7 +1734,7 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1949,7 +1811,7 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2026,7 +1888,7 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2103,7 +1965,7 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2180,7 +2042,7 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2216,7 +2078,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>-1</v>
@@ -2257,7 +2119,7 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2334,7 +2196,7 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2411,7 +2273,7 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2447,7 +2309,7 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -2488,7 +2350,7 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2565,7 +2427,7 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2642,7 +2504,7 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2719,7 +2581,7 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2755,7 +2617,7 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -2796,7 +2658,7 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2832,7 +2694,7 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -2873,7 +2735,7 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2909,7 +2771,7 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -2950,7 +2812,7 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -3027,7 +2889,7 @@
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3063,7 +2925,7 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>6</v>
@@ -3104,7 +2966,7 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3140,7 +3002,7 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -3181,7 +3043,7 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3217,7 +3079,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>6</v>
@@ -3368,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -3427,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -3483,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -3536,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -3595,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -3654,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -3713,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3772,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3831,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3890,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3949,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4008,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4067,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4126,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4185,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4244,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -4303,7 +4165,7 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -4362,7 +4224,7 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -4421,7 +4283,7 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -4480,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -4539,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -4598,7 +4460,7 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -4716,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -4775,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4834,7 +4696,7 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4893,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4952,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -5011,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -5070,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -5113,6 +4975,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5163,11 +5027,11 @@
       <c r="E2">
         <v>17</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>40</v>
       </c>
-      <c r="G2">
-        <v>56.67</v>
+      <c r="G2" s="2">
+        <v>56.7</v>
       </c>
       <c r="H2">
         <v>6.1</v>
@@ -5175,8 +5039,8 @@
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>3.33</v>
+      <c r="J2" s="2">
+        <v>3.3</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5195,11 +5059,11 @@
       <c r="E3">
         <v>5</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>80</v>
       </c>
-      <c r="G3">
-        <v>16.67</v>
+      <c r="G3" s="2">
+        <v>16.7</v>
       </c>
       <c r="H3">
         <v>7.1</v>
@@ -5207,77 +5071,77 @@
       <c r="I3">
         <v>1</v>
       </c>
-      <c r="J3">
-        <v>3.33</v>
+      <c r="J3" s="2">
+        <v>3.3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>86.20999999999999</v>
-      </c>
-      <c r="G4">
-        <v>10.34</v>
+        <v>6</v>
+      </c>
+      <c r="F4" s="2">
+        <v>80</v>
+      </c>
+      <c r="G4" s="2">
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3.45</v>
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>86.67</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
+      <c r="F5" s="2">
+        <v>86.2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10.3</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
-      <c r="J5">
-        <v>3.33</v>
+      <c r="J5" s="2">
+        <v>3.4</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5286,30 +5150,30 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>93.33</v>
-      </c>
-      <c r="G6">
-        <v>3.33</v>
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>86.7</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>6.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
-      <c r="J6">
-        <v>3.33</v>
+      <c r="J6" s="2">
+        <v>3.3</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -5321,22 +5185,22 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>93.33</v>
-      </c>
-      <c r="G7">
-        <v>6.67</v>
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>93.3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3.3</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>6.1</v>
       </c>
       <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -5410,7 +5274,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5450,7 +5314,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5470,7 +5334,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -5480,548 +5344,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920048</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>21330051920029</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>21330051920031</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>19330051920361</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>21330051920034</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>20330051920117</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>21330051920035</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>21330051920036</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>21330051920037</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>21330051920038</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>21330051920390</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>21330051920040</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>21330051920041</v>
-      </c>
-      <c r="B14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>21330051920043</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>21330051920045</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>21330051920046</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>21330051920047</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>21330051920050</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>130</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>21330051920051</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" t="s">
-        <v>131</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>21330051920054</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
-        <v>132</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>21330051920055</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" t="s">
-        <v>133</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>21330051920056</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>21330051920057</v>
-      </c>
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>21330051920058</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>21330051920059</v>
-      </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" t="s">
-        <v>137</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>21330051920060</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" t="s">
-        <v>138</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>21330051920062</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" t="s">
-        <v>139</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>21330051920063</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>21330051920065</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>103</v>
-      </c>
-      <c r="D30" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>21330051920067</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>113</v>
-      </c>
-      <c r="D31" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6053,16 +5376,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920036</v>
+        <v>21330051920029</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6076,22 +5399,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920036</v>
+        <v>21330051920031</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6099,16 +5422,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920029</v>
+        <v>21330051920035</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6122,16 +5445,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920031</v>
+        <v>21330051920390</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -6145,16 +5468,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920035</v>
+        <v>21330051920046</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -6168,16 +5491,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920390</v>
+        <v>21330051920057</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -6191,16 +5514,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920046</v>
+        <v>21330051920059</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -6214,16 +5537,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920057</v>
+        <v>21330051920060</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -6237,16 +5560,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920059</v>
+        <v>21330051920062</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6260,16 +5583,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920060</v>
+        <v>21330051920063</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -6283,16 +5606,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920062</v>
+        <v>21330051920067</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -6301,52 +5624,6 @@
         <v>54</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920063</v>
-      </c>
-      <c r="B13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920067</v>
-      </c>
-      <c r="B14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" t="s">
-        <v>142</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20222.xlsx
+++ b/grupos/4ARHV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -191,12 +191,12 @@
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
@@ -233,7 +233,7 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>HERRERA</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>ROMERO</t>
@@ -260,15 +260,12 @@
     <t>CELESTINO</t>
   </si>
   <si>
-    <t>SIERRA</t>
+    <t>ESTRADA</t>
   </si>
   <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -287,16 +284,13 @@
     <t>KARLA JIMENA</t>
   </si>
   <si>
-    <t>MIA ARANZA</t>
+    <t>GIOVANI</t>
   </si>
   <si>
     <t>INGRID CRISTEL</t>
   </si>
   <si>
     <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
   </si>
   <si>
     <t>KARLA JAZMIN</t>
@@ -813,13 +807,13 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -849,13 +843,13 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>5</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -890,13 +884,13 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>6</v>
@@ -964,13 +958,13 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -997,10 +991,10 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1032,13 +1026,13 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>9</v>
@@ -1109,13 +1103,13 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -1145,7 +1139,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -1186,13 +1180,13 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>8</v>
@@ -1222,13 +1216,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>5</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1263,13 +1257,13 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>5</v>
@@ -1299,7 +1293,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1340,13 +1334,13 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>5</v>
@@ -1382,7 +1376,7 @@
         <v>5</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1417,13 +1411,13 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>9</v>
@@ -1459,7 +1453,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1494,13 +1488,13 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>7</v>
@@ -1530,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1571,13 +1565,13 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>5</v>
@@ -1648,13 +1642,13 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>5</v>
@@ -1684,13 +1678,13 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>8</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1725,13 +1719,13 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>9</v>
@@ -1767,7 +1761,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1802,13 +1796,13 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>8</v>
@@ -1841,7 +1835,7 @@
         <v>8</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -1879,13 +1873,13 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>7</v>
@@ -1918,10 +1912,10 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -1956,13 +1950,13 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
         <v>8</v>
@@ -2015,13 +2009,13 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -2033,13 +2027,13 @@
         <v>-1</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>5</v>
@@ -2069,13 +2063,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2110,13 +2104,13 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>8</v>
@@ -2152,7 +2146,7 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2187,13 +2181,13 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>8</v>
@@ -2226,7 +2220,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2264,13 +2258,13 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>5</v>
@@ -2341,13 +2335,13 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>9</v>
@@ -2380,10 +2374,10 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2418,13 +2412,13 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>9</v>
@@ -2457,10 +2451,10 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2495,13 +2489,13 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>5</v>
@@ -2572,13 +2566,13 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>9</v>
@@ -2649,13 +2643,13 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -2685,13 +2679,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>5</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -2726,13 +2720,13 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
         <v>9</v>
@@ -2762,13 +2756,13 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -2803,13 +2797,13 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>8</v>
@@ -2845,7 +2839,7 @@
         <v>5</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -2880,13 +2874,13 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>9</v>
@@ -2916,13 +2910,13 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>5</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -2957,13 +2951,13 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>6</v>
@@ -2993,13 +2987,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>5</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>7</v>
@@ -3034,13 +3028,13 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
         <v>6</v>
@@ -3221,13 +3215,13 @@
         <v>93.3</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K4">
         <v>80</v>
@@ -3280,13 +3274,13 @@
         <v>106.7</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>96</v>
@@ -3336,13 +3330,13 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -3389,13 +3383,13 @@
         <v>66.7</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K7">
         <v>96</v>
@@ -3448,10 +3442,10 @@
         <v>86.7</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3507,13 +3501,13 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -3566,13 +3560,13 @@
         <v>86.7</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K10">
         <v>86</v>
@@ -3625,13 +3619,13 @@
         <v>60</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K11">
         <v>90</v>
@@ -3684,13 +3678,13 @@
         <v>120</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -3743,13 +3737,13 @@
         <v>93.3</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K13">
         <v>84</v>
@@ -3802,13 +3796,13 @@
         <v>73.3</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K14">
         <v>68</v>
@@ -3861,13 +3855,13 @@
         <v>80</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K15">
         <v>70</v>
@@ -3920,13 +3914,13 @@
         <v>120</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -3979,13 +3973,13 @@
         <v>80</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K17">
         <v>94</v>
@@ -4038,13 +4032,13 @@
         <v>80</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -4097,13 +4091,13 @@
         <v>120</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>96</v>
@@ -4138,13 +4132,13 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E20">
         <v>88</v>
@@ -4156,13 +4150,13 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K20">
         <v>92</v>
@@ -4215,13 +4209,13 @@
         <v>113.3</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -4274,13 +4268,13 @@
         <v>93.3</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K22">
         <v>92</v>
@@ -4333,13 +4327,13 @@
         <v>40</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K23">
         <v>70</v>
@@ -4392,13 +4386,13 @@
         <v>120</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -4451,13 +4445,13 @@
         <v>120</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -4510,10 +4504,10 @@
         <v>46.7</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4569,13 +4563,13 @@
         <v>73.3</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>98</v>
@@ -4628,13 +4622,13 @@
         <v>106.7</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -4687,13 +4681,13 @@
         <v>113.3</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -4746,13 +4740,13 @@
         <v>113.3</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -4805,13 +4799,13 @@
         <v>120</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -4864,13 +4858,13 @@
         <v>80</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K32">
         <v>90</v>
@@ -4923,13 +4917,13 @@
         <v>60</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>151.4</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K33">
         <v>90</v>
@@ -5022,25 +5016,25 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="2">
-        <v>40</v>
+        <v>46.7</v>
       </c>
       <c r="G2" s="2">
-        <v>56.7</v>
+        <v>53.3</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5057,22 +5051,22 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
         <v>80</v>
       </c>
       <c r="G3" s="2">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5109,66 +5103,66 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>25</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>86.2</v>
+        <v>83.3</v>
       </c>
       <c r="G5" s="2">
-        <v>10.3</v>
+        <v>16.7</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>86.7</v>
+        <v>86.2</v>
       </c>
       <c r="G6" s="2">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6" s="2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -5210,7 +5204,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5251,10 +5245,10 @@
         <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5271,69 +5265,9 @@
         <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920048</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920048</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920048</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
         <v>58</v>
       </c>
     </row>
@@ -5344,7 +5278,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5385,7 +5319,7 @@
         <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5408,7 +5342,7 @@
         <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -5431,7 +5365,7 @@
         <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5454,7 +5388,7 @@
         <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -5468,7 +5402,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920046</v>
+        <v>21330051920041</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
@@ -5477,13 +5411,13 @@
         <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5500,7 +5434,7 @@
         <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -5523,7 +5457,7 @@
         <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5537,16 +5471,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920060</v>
+        <v>21330051920062</v>
       </c>
       <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
         <v>72</v>
       </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5560,16 +5494,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920062</v>
+        <v>21330051920063</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5583,16 +5517,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920063</v>
+        <v>21330051920067</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
         <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -5601,29 +5535,6 @@
         <v>54</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920067</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20222.xlsx
+++ b/grupos/4ARHV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -185,6 +185,9 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Gomez Lopez Javier</t>
   </si>
   <si>
@@ -197,9 +200,6 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,6 +221,15 @@
     <t>MICHEL</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
     <t>ANDRADE</t>
   </si>
   <si>
@@ -230,18 +239,9 @@
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
     <t>TLAXCALTECATL</t>
   </si>
   <si>
@@ -251,27 +251,36 @@
     <t>VEGA</t>
   </si>
   <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
     <t>MARISOL</t>
   </si>
   <si>
@@ -281,16 +290,7 @@
     <t>GABRIELA ELIZABET</t>
   </si>
   <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
     <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
   </si>
   <si>
     <t>KARLA JAZMIN</t>
@@ -819,7 +819,7 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -896,7 +896,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -970,7 +970,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1000,7 +1000,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1038,7 +1038,7 @@
         <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1115,7 +1115,7 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1151,7 +1151,7 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1192,7 +1192,7 @@
         <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1228,7 +1228,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1269,7 +1269,7 @@
         <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1305,7 +1305,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1346,7 +1346,7 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1382,7 +1382,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1423,7 +1423,7 @@
         <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1500,7 +1500,7 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1536,7 +1536,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1577,7 +1577,7 @@
         <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1654,7 +1654,7 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1690,7 +1690,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1731,7 +1731,7 @@
         <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1808,7 +1808,7 @@
         <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1844,7 +1844,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -1885,7 +1885,7 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -1921,7 +1921,7 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -1962,7 +1962,7 @@
         <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2021,7 +2021,7 @@
         <v>6</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -2039,7 +2039,7 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2075,7 +2075,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>-1</v>
@@ -2116,7 +2116,7 @@
         <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2152,7 +2152,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2193,7 +2193,7 @@
         <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2270,7 +2270,7 @@
         <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2306,7 +2306,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2347,7 +2347,7 @@
         <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2383,7 +2383,7 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2424,7 +2424,7 @@
         <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2460,7 +2460,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2501,7 +2501,7 @@
         <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2537,7 +2537,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2578,7 +2578,7 @@
         <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2614,7 +2614,7 @@
         <v>9</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2655,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2732,7 +2732,7 @@
         <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2768,7 +2768,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -2809,7 +2809,7 @@
         <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -2845,7 +2845,7 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -2886,7 +2886,7 @@
         <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -2963,7 +2963,7 @@
         <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -2999,7 +2999,7 @@
         <v>7</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3040,7 +3040,7 @@
         <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3227,7 +3227,7 @@
         <v>80</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -3286,7 +3286,7 @@
         <v>96</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -3342,7 +3342,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3395,7 +3395,7 @@
         <v>96</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -3454,7 +3454,7 @@
         <v>60</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>86</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -3631,7 +3631,7 @@
         <v>90</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>84</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -3808,7 +3808,7 @@
         <v>68</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>70</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -3926,7 +3926,7 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -3985,7 +3985,7 @@
         <v>94</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -4044,7 +4044,7 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -4103,7 +4103,7 @@
         <v>96</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -4144,7 +4144,7 @@
         <v>88</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4162,7 +4162,7 @@
         <v>92</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>92</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -4339,7 +4339,7 @@
         <v>70</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -4398,7 +4398,7 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -4457,7 +4457,7 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -4575,7 +4575,7 @@
         <v>98</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -4634,7 +4634,7 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -4693,7 +4693,7 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -4752,7 +4752,7 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -4811,7 +4811,7 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -4870,7 +4870,7 @@
         <v>90</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -4929,7 +4929,7 @@
         <v>90</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -5039,7 +5039,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5048,19 +5048,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="G3" s="2">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5092,7 +5092,7 @@
         <v>20</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5103,7 +5103,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5112,19 +5112,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="G5" s="2">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5135,66 +5135,66 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>25</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>86.2</v>
+        <v>83.3</v>
       </c>
       <c r="G6" s="2">
-        <v>10.3</v>
+        <v>16.7</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>93.3</v>
+        <v>86.2</v>
       </c>
       <c r="G7" s="2">
-        <v>3.3</v>
+        <v>10.3</v>
       </c>
       <c r="H7">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7" s="2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>
@@ -5204,7 +5204,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5245,30 +5245,10 @@
         <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920048</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -5278,7 +5258,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5310,7 +5290,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920029</v>
+        <v>21330051920390</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
@@ -5333,22 +5313,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920031</v>
+        <v>21330051920390</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5356,22 +5336,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920035</v>
+        <v>21330051920041</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5379,22 +5359,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920390</v>
+        <v>21330051920041</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5402,22 +5382,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920041</v>
+        <v>21330051920059</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5425,22 +5405,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920057</v>
+        <v>21330051920059</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5448,16 +5428,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920059</v>
+        <v>21330051920029</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5471,16 +5451,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920062</v>
+        <v>21330051920031</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5494,16 +5474,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920063</v>
+        <v>21330051920035</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5517,16 +5497,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920067</v>
+        <v>21330051920057</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -5535,6 +5515,75 @@
         <v>54</v>
       </c>
       <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920062</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920063</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920067</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20222.xlsx
+++ b/grupos/4ARHV - Estadisticos 20222.xlsx
@@ -194,10 +194,10 @@
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>NC</t>
@@ -822,7 +822,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -858,7 +858,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -899,7 +899,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1041,7 +1041,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1077,7 +1077,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1118,7 +1118,7 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1154,7 +1154,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1195,7 +1195,7 @@
         <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1231,7 +1231,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1272,7 +1272,7 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1308,7 +1308,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1349,7 +1349,7 @@
         <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1426,7 +1426,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1503,7 +1503,7 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1539,7 +1539,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1580,7 +1580,7 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1657,7 +1657,7 @@
         <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1693,7 +1693,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1734,7 +1734,7 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1811,7 +1811,7 @@
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1847,7 +1847,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1888,7 +1888,7 @@
         <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1924,7 +1924,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1965,7 +1965,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2001,7 +2001,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2119,7 +2119,7 @@
         <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2155,7 +2155,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2196,7 +2196,7 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2232,7 +2232,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2273,7 +2273,7 @@
         <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2350,7 +2350,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2386,7 +2386,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2427,7 +2427,7 @@
         <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2463,7 +2463,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2581,7 +2581,7 @@
         <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2617,7 +2617,7 @@
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2658,7 +2658,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2694,7 +2694,7 @@
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2735,7 +2735,7 @@
         <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2812,7 +2812,7 @@
         <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2889,7 +2889,7 @@
         <v>6</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2966,7 +2966,7 @@
         <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3002,7 +3002,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3043,7 +3043,7 @@
         <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3079,7 +3079,7 @@
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3230,7 +3230,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -3575,7 +3575,7 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -3634,7 +3634,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3752,7 +3752,7 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         <v>60</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3870,7 +3870,7 @@
         <v>70</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3929,7 +3929,7 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4106,7 +4106,7 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4224,7 +4224,7 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4283,7 +4283,7 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>50</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -4401,7 +4401,7 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -4460,7 +4460,7 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -4578,7 +4578,7 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -4637,7 +4637,7 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -4696,7 +4696,7 @@
         <v>100</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -4755,7 +4755,7 @@
         <v>100</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -4814,7 +4814,7 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -4932,7 +4932,7 @@
         <v>100</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5135,66 +5135,66 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>83.3</v>
+        <v>82.8</v>
       </c>
       <c r="G6" s="2">
-        <v>16.7</v>
+        <v>13.8</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>25</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>86.2</v>
+        <v>83.3</v>
       </c>
       <c r="G7" s="2">
-        <v>10.3</v>
+        <v>16.7</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5248,7 +5248,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ARHV - Estadisticos 20222.xlsx
+++ b/grupos/4ARHV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -194,12 +194,12 @@
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -210,15 +210,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
   </si>
   <si>
     <t>FLORES</t>
@@ -2024,7 +2015,7 @@
         <v>6</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -2042,7 +2033,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2078,7 +2069,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -4147,7 +4138,7 @@
         <v>100</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H20">
         <v>151.4</v>
@@ -4165,7 +4156,7 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -5135,60 +5126,60 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>82.8</v>
+        <v>83.3</v>
       </c>
       <c r="G6" s="2">
-        <v>13.8</v>
+        <v>16.7</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>25</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>83.3</v>
+        <v>86.2</v>
       </c>
       <c r="G7" s="2">
-        <v>16.7</v>
+        <v>13.8</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5204,7 +5195,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5229,26 +5220,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920048</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -5293,13 +5264,13 @@
         <v>21330051920390</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5316,13 +5287,13 @@
         <v>21330051920390</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5339,13 +5310,13 @@
         <v>21330051920041</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5362,13 +5333,13 @@
         <v>21330051920041</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5385,13 +5356,13 @@
         <v>21330051920059</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5408,13 +5379,13 @@
         <v>21330051920059</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5431,13 +5402,13 @@
         <v>21330051920029</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5454,13 +5425,13 @@
         <v>21330051920031</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5477,13 +5448,13 @@
         <v>21330051920035</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5500,13 +5471,13 @@
         <v>21330051920057</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -5523,13 +5494,13 @@
         <v>21330051920062</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -5546,13 +5517,13 @@
         <v>21330051920063</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -5569,13 +5540,13 @@
         <v>21330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>

--- a/grupos/4ARHV - Estadisticos 20222.xlsx
+++ b/grupos/4ARHV - Estadisticos 20222.xlsx
@@ -3188,10 +3188,10 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>90</v>
@@ -3203,43 +3203,43 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="H4">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K4">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>33.3</v>
+        <v>52.8</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3247,10 +3247,10 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C5">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -3262,43 +3262,43 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>106.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H5">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>120</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3306,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C6">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -3321,10 +3321,10 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I6">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3336,19 +3336,19 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3356,10 +3356,10 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C7">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>80</v>
@@ -3371,43 +3371,43 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="H7">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I7">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>80</v>
       </c>
       <c r="K7">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3415,10 +3415,10 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C8">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>80</v>
@@ -3430,43 +3430,43 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>86.7</v>
+        <v>72.2</v>
       </c>
       <c r="H8">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I8">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K8">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3474,10 +3474,10 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C9">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>90</v>
@@ -3489,13 +3489,13 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="H9">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I9">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>90</v>
@@ -3507,25 +3507,25 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>113.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3533,10 +3533,10 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C10">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>80</v>
@@ -3548,43 +3548,43 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>86.7</v>
+        <v>72.2</v>
       </c>
       <c r="H10">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I10">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>80</v>
       </c>
       <c r="K10">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L10">
         <v>100</v>
       </c>
       <c r="M10">
-        <v>113.3</v>
+        <v>83.3</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3592,10 +3592,10 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C11">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>90</v>
@@ -3607,43 +3607,43 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H11">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I11">
-        <v>75</v>
+        <v>81.8</v>
       </c>
       <c r="J11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K11">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3651,10 +3651,10 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C12">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>100</v>
@@ -3666,43 +3666,43 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I12">
-        <v>110</v>
+        <v>94.5</v>
       </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>113.3</v>
+        <v>97.2</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3710,10 +3710,10 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C13">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -3725,19 +3725,19 @@
         <v>100</v>
       </c>
       <c r="G13">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="H13">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I13">
-        <v>110</v>
+        <v>94.5</v>
       </c>
       <c r="J13">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K13">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -3746,22 +3746,22 @@
         <v>66.7</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3769,10 +3769,10 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C14">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>80</v>
@@ -3784,43 +3784,43 @@
         <v>50</v>
       </c>
       <c r="G14">
-        <v>73.3</v>
+        <v>61.1</v>
       </c>
       <c r="H14">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I14">
-        <v>110</v>
+        <v>94.5</v>
       </c>
       <c r="J14">
         <v>80</v>
       </c>
       <c r="K14">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M14">
-        <v>66.7</v>
+        <v>58.3</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3828,10 +3828,10 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>80</v>
@@ -3843,43 +3843,43 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="H15">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I15">
-        <v>120</v>
+        <v>98.2</v>
       </c>
       <c r="J15">
         <v>80</v>
       </c>
       <c r="K15">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="L15">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="M15">
-        <v>93.3</v>
+        <v>72.2</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3887,10 +3887,10 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C16">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>100</v>
@@ -3902,13 +3902,13 @@
         <v>100</v>
       </c>
       <c r="G16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H16">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I16">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -3920,25 +3920,25 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3946,10 +3946,10 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C17">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>90</v>
@@ -3961,43 +3961,43 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="H17">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I17">
-        <v>115</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="J17">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K17">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>106.7</v>
+        <v>77.8</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4005,10 +4005,10 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C18">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>80</v>
@@ -4020,43 +4020,43 @@
         <v>100</v>
       </c>
       <c r="G18">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="H18">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I18">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>80</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
-        <v>86.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4064,10 +4064,10 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C19">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -4079,43 +4079,43 @@
         <v>100</v>
       </c>
       <c r="G19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H19">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I19">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4123,10 +4123,10 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C20">
-        <v>125</v>
+        <v>83.3</v>
       </c>
       <c r="D20">
         <v>80</v>
@@ -4138,43 +4138,43 @@
         <v>100</v>
       </c>
       <c r="G20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H20">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I20">
-        <v>110</v>
+        <v>85.5</v>
       </c>
       <c r="J20">
         <v>80</v>
       </c>
       <c r="K20">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L20">
         <v>100</v>
       </c>
       <c r="M20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>85.5</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4182,10 +4182,10 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C21">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>90</v>
@@ -4197,16 +4197,16 @@
         <v>100</v>
       </c>
       <c r="G21">
-        <v>113.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H21">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I21">
-        <v>120</v>
+        <v>98.2</v>
       </c>
       <c r="J21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -4215,25 +4215,25 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>120</v>
+        <v>97.2</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4241,10 +4241,10 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C22">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>90</v>
@@ -4256,43 +4256,43 @@
         <v>100</v>
       </c>
       <c r="G22">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="H22">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I22">
-        <v>120</v>
+        <v>98.2</v>
       </c>
       <c r="J22">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K22">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L22">
         <v>100</v>
       </c>
       <c r="M22">
-        <v>120</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4300,10 +4300,10 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C23">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>80</v>
@@ -4315,43 +4315,43 @@
         <v>100</v>
       </c>
       <c r="G23">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="H23">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I23">
-        <v>50</v>
+        <v>72.7</v>
       </c>
       <c r="J23">
         <v>80</v>
       </c>
       <c r="K23">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L23">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M23">
-        <v>33.3</v>
+        <v>30.6</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4359,10 +4359,10 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C24">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>100</v>
@@ -4374,13 +4374,13 @@
         <v>100</v>
       </c>
       <c r="G24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H24">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I24">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -4392,25 +4392,25 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4418,10 +4418,10 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C25">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -4433,13 +4433,13 @@
         <v>100</v>
       </c>
       <c r="G25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H25">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I25">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -4451,25 +4451,25 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4477,10 +4477,10 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C26">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D26">
         <v>80</v>
@@ -4492,43 +4492,43 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>46.7</v>
+        <v>38.9</v>
       </c>
       <c r="H26">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I26">
-        <v>75</v>
+        <v>54.5</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L26">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4536,10 +4536,10 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C27">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>90</v>
@@ -4551,43 +4551,43 @@
         <v>100</v>
       </c>
       <c r="G27">
-        <v>73.3</v>
+        <v>61.1</v>
       </c>
       <c r="H27">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K27">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>120</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4595,10 +4595,10 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C28">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>90</v>
@@ -4610,43 +4610,43 @@
         <v>100</v>
       </c>
       <c r="G28">
-        <v>106.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H28">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I28">
-        <v>110</v>
+        <v>94.5</v>
       </c>
       <c r="J28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L28">
         <v>100</v>
       </c>
       <c r="M28">
-        <v>120</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4654,10 +4654,10 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C29">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>90</v>
@@ -4669,16 +4669,16 @@
         <v>100</v>
       </c>
       <c r="G29">
-        <v>113.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H29">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I29">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -4687,25 +4687,25 @@
         <v>100</v>
       </c>
       <c r="M29">
-        <v>120</v>
+        <v>97.2</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4713,10 +4713,10 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C30">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>100</v>
@@ -4728,13 +4728,13 @@
         <v>100</v>
       </c>
       <c r="G30">
-        <v>113.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H30">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I30">
-        <v>110</v>
+        <v>94.5</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -4746,25 +4746,25 @@
         <v>100</v>
       </c>
       <c r="M30">
-        <v>120</v>
+        <v>97.2</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4772,10 +4772,10 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C31">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>90</v>
@@ -4787,16 +4787,16 @@
         <v>100</v>
       </c>
       <c r="G31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H31">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I31">
-        <v>110</v>
+        <v>94.5</v>
       </c>
       <c r="J31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -4805,25 +4805,25 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4831,10 +4831,10 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C32">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>90</v>
@@ -4846,43 +4846,43 @@
         <v>100</v>
       </c>
       <c r="G32">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="H32">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J32">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K32">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32">
-        <v>86.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -4890,10 +4890,10 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="C33">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>90</v>
@@ -4905,43 +4905,43 @@
         <v>100</v>
       </c>
       <c r="G33">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H33">
-        <v>151.4</v>
+        <v>100</v>
       </c>
       <c r="I33">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J33">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K33">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L33">
         <v>100</v>
       </c>
       <c r="M33">
-        <v>106.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ARHV - Estadisticos 20222.xlsx
+++ b/grupos/4ARHV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="97">
   <si>
     <t>Materia</t>
   </si>
@@ -185,18 +185,18 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Gomez Lopez Javier</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Gomez Lopez Javier</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -212,27 +212,33 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>ROMANOS</t>
   </si>
   <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>TLAXCALTECATL</t>
   </si>
   <si>
@@ -242,46 +248,58 @@
     <t>VEGA</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>CELESTINO</t>
   </si>
   <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABET</t>
+  </si>
+  <si>
     <t>KARLA JIMENA</t>
   </si>
   <si>
-    <t>GIOVANI</t>
+    <t>INGRID CRISTEL</t>
   </si>
   <si>
     <t>DANIELA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABET</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
   </si>
   <si>
     <t>KARLA JAZMIN</t>
@@ -816,34 +834,34 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>7</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -893,19 +911,19 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -917,13 +935,13 @@
         <v>5</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>8</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -964,28 +982,28 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>7</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1035,19 +1053,19 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1059,7 +1077,7 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1112,19 +1130,19 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1142,7 +1160,7 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1189,19 +1207,19 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1266,37 +1284,37 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>5</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1343,19 +1361,19 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1367,7 +1385,7 @@
         <v>5</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1420,19 +1438,19 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1444,7 +1462,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1497,25 +1515,25 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1524,10 +1542,10 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1574,25 +1592,25 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -1601,7 +1619,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1651,25 +1669,25 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1678,7 +1696,7 @@
         <v>5</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1728,37 +1746,37 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1805,34 +1823,34 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>7</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -1882,25 +1900,25 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -1909,10 +1927,10 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -1959,25 +1977,25 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -1986,7 +2004,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2036,19 +2054,19 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2063,10 +2081,10 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2113,19 +2131,19 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2134,7 +2152,7 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2190,25 +2208,25 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2220,7 +2238,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2267,19 +2285,19 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2344,19 +2362,19 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2365,13 +2383,13 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>8</v>
@@ -2421,19 +2439,19 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2498,19 +2516,19 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2575,19 +2593,19 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2605,7 +2623,7 @@
         <v>9</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2652,25 +2670,25 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -2729,28 +2747,28 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -2806,19 +2824,19 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -2830,13 +2848,13 @@
         <v>5</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>8</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -2883,37 +2901,37 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>5</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>9</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -2960,37 +2978,37 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>5</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>7</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3037,31 +3055,31 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>6</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3227,13 +3245,13 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="P4">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q4">
-        <v>83</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3286,13 +3304,13 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -3345,7 +3363,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3395,13 +3413,13 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P7">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -3457,10 +3475,10 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="Q8">
-        <v>70</v>
+        <v>44.3</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -3516,7 +3534,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3572,13 +3590,13 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P10">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q10">
-        <v>87</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -3631,16 +3649,16 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>81.8</v>
+        <v>68.8</v>
       </c>
       <c r="P11">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q11">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="S11">
         <v>66.7</v>
@@ -3690,13 +3708,13 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="P12">
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -3749,13 +3767,13 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>94.5</v>
+        <v>93.8</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q13">
-        <v>86</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -3808,16 +3826,16 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>94.5</v>
+        <v>77.5</v>
       </c>
       <c r="P14">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q14">
-        <v>70</v>
+        <v>44.3</v>
       </c>
       <c r="R14">
-        <v>55</v>
+        <v>34.4</v>
       </c>
       <c r="S14">
         <v>58.3</v>
@@ -3867,16 +3885,16 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>98.2</v>
+        <v>92.5</v>
       </c>
       <c r="P15">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q15">
-        <v>81</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="R15">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="S15">
         <v>72.2</v>
@@ -3926,7 +3944,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -3985,13 +4003,13 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>96.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="P17">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q17">
-        <v>88</v>
+        <v>84.2</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4044,13 +4062,13 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P18">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q18">
-        <v>95</v>
+        <v>89.2</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4106,10 +4124,10 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q19">
-        <v>98</v>
+        <v>96.8</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4162,13 +4180,13 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>85.5</v>
+        <v>86.3</v>
       </c>
       <c r="P20">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q20">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -4221,10 +4239,10 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>98.2</v>
+        <v>96.3</v>
       </c>
       <c r="P21">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4280,13 +4298,13 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>98.2</v>
+        <v>95</v>
       </c>
       <c r="P22">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q22">
-        <v>95</v>
+        <v>93.7</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -4339,16 +4357,16 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>72.7</v>
+        <v>50</v>
       </c>
       <c r="P23">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q23">
-        <v>73</v>
+        <v>46.2</v>
       </c>
       <c r="R23">
-        <v>75</v>
+        <v>46.9</v>
       </c>
       <c r="S23">
         <v>30.6</v>
@@ -4398,7 +4416,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -4463,7 +4481,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -4516,16 +4534,16 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>54.5</v>
+        <v>37.5</v>
       </c>
       <c r="P26">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="Q26">
-        <v>14</v>
+        <v>8.9</v>
       </c>
       <c r="R26">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="S26">
         <v>19.4</v>
@@ -4575,13 +4593,13 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>90.90000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="P27">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="Q27">
-        <v>96</v>
+        <v>96.8</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -4634,13 +4652,13 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>94.5</v>
+        <v>93.8</v>
       </c>
       <c r="P28">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="Q28">
-        <v>96</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -4696,10 +4714,10 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -4752,7 +4770,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>94.5</v>
+        <v>92.5</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -4811,10 +4829,10 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>94.5</v>
+        <v>93.8</v>
       </c>
       <c r="P31">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -4870,13 +4888,13 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>90.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="P32">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q32">
-        <v>87</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -4929,13 +4947,13 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="P33">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q33">
-        <v>88</v>
+        <v>87.3</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -5007,16 +5025,16 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" s="2">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="G2" s="2">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>6.3</v>
@@ -5030,7 +5048,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5039,19 +5057,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>66.7</v>
+        <v>76.7</v>
       </c>
       <c r="G3" s="2">
-        <v>33.3</v>
+        <v>23.3</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5062,7 +5080,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5094,7 +5112,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5103,19 +5121,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="G5" s="2">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5126,7 +5144,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5147,7 +5165,7 @@
         <v>16.7</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5229,7 +5247,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5261,22 +5279,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920390</v>
+        <v>21330051920031</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5284,22 +5302,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920390</v>
+        <v>21330051920031</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5307,22 +5325,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920041</v>
+        <v>21330051920036</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5330,22 +5348,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920041</v>
+        <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5353,22 +5371,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920059</v>
+        <v>21330051920041</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5376,22 +5394,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920059</v>
+        <v>21330051920041</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5399,22 +5417,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920029</v>
+        <v>21330051920048</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5422,16 +5440,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920031</v>
+        <v>21330051920048</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5445,16 +5463,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920035</v>
+        <v>21330051920029</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5468,16 +5486,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920057</v>
+        <v>21330051920035</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -5491,16 +5509,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920062</v>
+        <v>21330051920390</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -5514,16 +5532,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920063</v>
+        <v>21330051920057</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -5537,16 +5555,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920067</v>
+        <v>21330051920059</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -5555,6 +5573,75 @@
         <v>54</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920062</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920063</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920067</v>
+      </c>
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20222.xlsx
+++ b/grupos/4ARHV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="101">
   <si>
     <t>Materia</t>
   </si>
@@ -185,6 +185,9 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
@@ -197,9 +200,6 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,25 +212,31 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>COMIHUA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>FLORES</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>VEGA</t>
+  </si>
+  <si>
     <t>ANDRADE</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
   </si>
   <si>
     <t>ROMERO</t>
@@ -245,25 +251,28 @@
     <t>TETLA</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
+    <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ESTRADA</t>
+    <t>CELESTINO</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
   </si>
   <si>
     <t>TEZOCO</t>
@@ -272,28 +281,31 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
     <t>ALEJANDRO GABRIEL</t>
   </si>
   <si>
-    <t>GIOVANI</t>
+    <t>KARLA JIMENA</t>
   </si>
   <si>
     <t>MICHEL</t>
   </si>
   <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
     <t>MARISOL</t>
   </si>
   <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
     <t>GABRIELA ELIZABET</t>
   </si>
   <si>
-    <t>KARLA JIMENA</t>
+    <t>ZURY BETZABE</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
   </si>
   <si>
     <t>INGRID CRISTEL</t>
@@ -308,7 +320,7 @@
     <t>YAZURI</t>
   </si>
   <si>
-    <t>HANIA ZARETH</t>
+    <t>XIMENA</t>
   </si>
 </sst>
 </file>
@@ -849,7 +861,7 @@
         <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -867,7 +879,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -926,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>7</v>
@@ -1068,7 +1080,7 @@
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1086,7 +1098,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1145,7 +1157,7 @@
         <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1163,7 +1175,7 @@
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1222,7 +1234,7 @@
         <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>7</v>
@@ -1240,7 +1252,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1299,7 +1311,7 @@
         <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>5</v>
@@ -1376,7 +1388,7 @@
         <v>5</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1453,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1530,7 +1542,7 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -1548,7 +1560,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1607,7 +1619,7 @@
         <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>6</v>
@@ -1684,7 +1696,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>6</v>
@@ -1702,7 +1714,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1761,7 +1773,7 @@
         <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1838,7 +1850,7 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -1856,7 +1868,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1915,7 +1927,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -1933,7 +1945,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1992,7 +2004,7 @@
         <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2069,7 +2081,7 @@
         <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2146,7 +2158,7 @@
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2223,7 +2235,7 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2300,7 +2312,7 @@
         <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T23">
         <v>5</v>
@@ -2377,7 +2389,7 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2454,7 +2466,7 @@
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2531,7 +2543,7 @@
         <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T26">
         <v>5</v>
@@ -2608,7 +2620,7 @@
         <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -2685,7 +2697,7 @@
         <v>7</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>6</v>
@@ -2762,7 +2774,7 @@
         <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2839,7 +2851,7 @@
         <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -2916,7 +2928,7 @@
         <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -2993,7 +3005,7 @@
         <v>6</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>6</v>
@@ -3011,7 +3023,7 @@
         <v>6</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3070,7 +3082,7 @@
         <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
         <v>7</v>
@@ -3088,7 +3100,7 @@
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3257,7 +3269,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>52.8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3316,7 +3328,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>94.40000000000001</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3425,7 +3437,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>69.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3484,7 +3496,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3543,7 +3555,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3602,7 +3614,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>83.3</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3661,7 +3673,7 @@
         <v>62.5</v>
       </c>
       <c r="S11">
-        <v>66.7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3720,7 +3732,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>97.2</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3779,7 +3791,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3838,7 +3850,7 @@
         <v>34.4</v>
       </c>
       <c r="S14">
-        <v>58.3</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4015,7 +4027,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>77.8</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4074,7 +4086,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>69.40000000000001</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4133,7 +4145,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4251,7 +4263,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4310,7 +4322,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>88.90000000000001</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4369,7 +4381,7 @@
         <v>46.9</v>
       </c>
       <c r="S23">
-        <v>30.6</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4546,7 +4558,7 @@
         <v>50</v>
       </c>
       <c r="S26">
-        <v>19.4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4605,7 +4617,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>80.59999999999999</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4664,7 +4676,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>94.40000000000001</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4723,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4782,7 +4794,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4900,7 +4912,7 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>69.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -4959,7 +4971,7 @@
         <v>100</v>
       </c>
       <c r="S33">
-        <v>69.40000000000001</v>
+        <v>68.5</v>
       </c>
     </row>
   </sheetData>
@@ -5048,28 +5060,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
       </c>
       <c r="C3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>76.7</v>
+        <v>55.2</v>
       </c>
       <c r="G3" s="2">
-        <v>23.3</v>
+        <v>44.8</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5080,7 +5092,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5089,19 +5101,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>80</v>
+        <v>76.7</v>
       </c>
       <c r="G4" s="2">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5112,7 +5124,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5121,19 +5133,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="G5" s="2">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5144,7 +5156,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5165,7 +5177,7 @@
         <v>16.7</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5176,28 +5188,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>25</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>86.2</v>
+        <v>83.3</v>
       </c>
       <c r="G7" s="2">
-        <v>13.8</v>
+        <v>16.7</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5247,7 +5259,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5279,22 +5291,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920031</v>
+        <v>21330051920036</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5302,22 +5314,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920031</v>
+        <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5325,22 +5337,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920036</v>
+        <v>21330051920390</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5348,22 +5360,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920036</v>
+        <v>21330051920390</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5371,22 +5383,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920041</v>
+        <v>21330051920048</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5394,22 +5406,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920041</v>
+        <v>21330051920048</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5417,22 +5429,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920048</v>
+        <v>21330051920067</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5440,22 +5452,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920048</v>
+        <v>21330051920067</v>
       </c>
       <c r="B9" t="s">
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5469,10 +5481,10 @@
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5486,22 +5498,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920035</v>
+        <v>21330051920034</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5509,16 +5521,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920390</v>
+        <v>21330051920035</v>
       </c>
       <c r="B12" t="s">
         <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -5532,22 +5544,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920057</v>
+        <v>21330051920045</v>
       </c>
       <c r="B13" t="s">
         <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5555,22 +5567,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920059</v>
+        <v>21330051920046</v>
       </c>
       <c r="B14" t="s">
         <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5578,7 +5590,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920062</v>
+        <v>21330051920057</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
@@ -5587,7 +5599,7 @@
         <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -5601,16 +5613,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920063</v>
+        <v>21330051920059</v>
       </c>
       <c r="B16" t="s">
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -5624,16 +5636,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920067</v>
+        <v>21330051920062</v>
       </c>
       <c r="B17" t="s">
         <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -5642,6 +5654,52 @@
         <v>54</v>
       </c>
       <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920063</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920065</v>
+      </c>
+      <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19">
         <v>5</v>
       </c>
     </row>
